--- a/quizzes/peinture-15e-niveau1.xlsx
+++ b/quizzes/peinture-15e-niveau1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers excel terminés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{30882A05-25EF-4066-9704-0F19F9F5AFA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05153039-1950-4136-A2BA-59603222C908}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12690" yWindow="180" windowWidth="14235" windowHeight="15135" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quiz peinture 15e" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="141">
   <si>
     <t>image</t>
   </si>
@@ -361,15 +361,6 @@
     <t>La Pêche miraculeuse</t>
   </si>
   <si>
-    <t>Stefan LOCHNER</t>
-  </si>
-  <si>
-    <t>Wallraf-Richartz Museum, Cologne</t>
-  </si>
-  <si>
-    <t>La Vierge au buisson de roses</t>
-  </si>
-  <si>
     <t>Piero di COSIMO</t>
   </si>
   <si>
@@ -424,12 +415,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/1c/Konrad_Witz_008.jpg/1280px-Konrad_Witz_008.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/72/Stefan_Lochner_Madonna_im_Rosenhag.jpg/1280px-Stefan_Lochner_Madonna_im_Rosenhag.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>vers 1440-1442</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/1f/Cosm%C3%A8_tura%2C_madonna_col_bambino_in_trono%2C_1475_ca._01.jpg/1280px-Cosm%C3%A8_tura%2C_madonna_col_bambino_in_trono%2C_1475_ca._01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -449,13 +434,22 @@
   </si>
   <si>
     <t>Musée Condé, Château de Chantilly </t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/b0/Annunciation_%28Leonardo%29_%28cropped%29.jpg/1280px-Annunciation_%28Leonardo%29_%28cropped%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Leonard de Vinci</t>
+  </si>
+  <si>
+    <t>Annonciation</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -487,8 +481,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -504,6 +505,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -558,7 +565,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -577,6 +584,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -880,7 +890,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="111.85546875" customWidth="1"/>
@@ -909,546 +919,552 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="4" t="s">
-        <v>5</v>
+        <v>125</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>6</v>
+        <v>106</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>7</v>
+        <v>126</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>9</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>14</v>
+      <c r="A3" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="4" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>24</v>
+      <c r="A5" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>28</v>
+      <c r="A6" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C6" s="8">
+        <v>1486</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="E8" s="6" t="s">
         <v>118</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="4" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="D9" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E9" s="5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>44</v>
+      <c r="E10" s="5" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>49</v>
+      <c r="A11" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="4" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>53</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>58</v>
+      <c r="A13" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="4" t="s">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="4" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B18" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C18" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D18" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E18" s="5" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="4" t="s">
+    <row r="19" spans="1:8">
+      <c r="A19" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B24" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C24" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D24" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E24" s="5" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="7" t="s">
+    <row r="25" spans="1:8">
+      <c r="A25" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="C26" s="8">
+        <v>1480</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="C30" s="11">
+        <v>1472</v>
+      </c>
+      <c r="D30" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12"/>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="B23" s="6" t="s">
+      <c r="B31" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C31" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="D31" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="E23" s="6" t="s">
+      <c r="E31" s="6" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C24" s="8">
-        <v>1486</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="C30" s="8">
-        <v>1480</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>138</v>
-      </c>
-    </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E31">
+    <sortCondition ref="B2:B31"/>
+  </sortState>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="A3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="A4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="A5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="A6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="A8" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="A9" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="A11" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="A12" r:id="rId9" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="A13" r:id="rId10" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="A14" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="A15" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="A16" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="A17" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="A21" r:id="rId15" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="A22" r:id="rId16" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="A7" r:id="rId17" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/aa/Mantegna_-_Ducal_Palace%2C_View_of_the_west_and_north_walls%2C_0sposi2.jpg/1280px-Mantegna_-_Ducal_Palace%2C_View_of_the_west_and_north_walls%2C_0sposi2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{4BD87EE3-F1B9-4C29-93BD-4722B4E7E508}"/>
-    <hyperlink ref="A18" r:id="rId18" xr:uid="{7CD0BC50-BC39-4E5C-B30C-5B70AC3F3F49}"/>
-    <hyperlink ref="A19" r:id="rId19" xr:uid="{DF729D38-2B26-42A6-B1C9-BCEF3CA9107F}"/>
-    <hyperlink ref="A20" r:id="rId20" xr:uid="{BFEF19CB-CD93-4056-B2F6-4FF4B1E8E638}"/>
-    <hyperlink ref="A23" r:id="rId21" display="https://upload.wikimedia.org/wikipedia/commons/thumb/c/c1/Accademia_-_Sogno_di_sant%27Orsola_-_Vittore_Carpaccio.jpg/1280px-Accademia_-_Sogno_di_sant%27Orsola_-_Vittore_Carpaccio.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{36E1FB7B-65AB-4F27-A267-9DCFA7068334}"/>
-    <hyperlink ref="A24" r:id="rId22" xr:uid="{133BF864-032D-430B-9B5D-C5ADBF31621F}"/>
-    <hyperlink ref="A26" r:id="rId23" xr:uid="{603E9B56-1E62-4A9E-A6BC-927D1CB41962}"/>
-    <hyperlink ref="A27" r:id="rId24" xr:uid="{F14E50B0-D9C0-48DB-931C-366DA60D26A5}"/>
-    <hyperlink ref="A28" r:id="rId25" xr:uid="{B46CDD11-F539-4CD8-8F01-99911F246E5E}"/>
-    <hyperlink ref="A29" r:id="rId26" xr:uid="{1EEED078-20CC-43D1-B1C9-991B04FF55F4}"/>
-    <hyperlink ref="A31" r:id="rId27" xr:uid="{358517C9-F96D-4001-A6D2-2579CAC07395}"/>
-    <hyperlink ref="A25" r:id="rId28" xr:uid="{A1B2AAD9-A8FD-4DBD-8E21-BF758D91F420}"/>
-    <hyperlink ref="A10" r:id="rId29" display="https://upload.wikimedia.org/wikipedia/commons/thumb/4/42/Madonna_and_Child_with_two_Angels_%28by_Filippo_Lippi%29_%E2%80%93_Galleria_degli_Uffizi%2C_Florence.jpg/960px-Madonna_and_Child_with_two_Angels_%28by_Filippo_Lippi%29_%E2%80%93_Galleria_degli_Uffizi%2C_Florence.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A9E81F97-D9BA-4EA8-8D6C-9CA4C0B8E7A9}"/>
-    <hyperlink ref="A30" r:id="rId30" display="https://upload.wikimedia.org/wikipedia/commons/thumb/1/1d/Piero_di_Cosimo_-_Portrait_de_femme_dit_de_Simonetta_Vespucci_-_Google_Art_Project.jpg/960px-Piero_di_Cosimo_-_Portrait_de_femme_dit_de_Simonetta_Vespucci_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{345345A4-5E6D-4024-8651-B74F4AB819D3}"/>
+    <hyperlink ref="A29" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="A21" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="A12" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="A25" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="A9" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="A14" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="A23" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="A4" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="A17" r:id="rId9" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="A28" r:id="rId10" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="A15" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="A16" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="A18" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="A24" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="A20" r:id="rId15" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="A27" r:id="rId16" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="A3" r:id="rId17" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/aa/Mantegna_-_Ducal_Palace%2C_View_of_the_west_and_north_walls%2C_0sposi2.jpg/1280px-Mantegna_-_Ducal_Palace%2C_View_of_the_west_and_north_walls%2C_0sposi2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{4BD87EE3-F1B9-4C29-93BD-4722B4E7E508}"/>
+    <hyperlink ref="A8" r:id="rId18" xr:uid="{7CD0BC50-BC39-4E5C-B30C-5B70AC3F3F49}"/>
+    <hyperlink ref="A5" r:id="rId19" xr:uid="{DF729D38-2B26-42A6-B1C9-BCEF3CA9107F}"/>
+    <hyperlink ref="A11" r:id="rId20" xr:uid="{BFEF19CB-CD93-4056-B2F6-4FF4B1E8E638}"/>
+    <hyperlink ref="A31" r:id="rId21" display="https://upload.wikimedia.org/wikipedia/commons/thumb/c/c1/Accademia_-_Sogno_di_sant%27Orsola_-_Vittore_Carpaccio.jpg/1280px-Accademia_-_Sogno_di_sant%27Orsola_-_Vittore_Carpaccio.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{36E1FB7B-65AB-4F27-A267-9DCFA7068334}"/>
+    <hyperlink ref="A6" r:id="rId22" xr:uid="{133BF864-032D-430B-9B5D-C5ADBF31621F}"/>
+    <hyperlink ref="A2" r:id="rId23" xr:uid="{603E9B56-1E62-4A9E-A6BC-927D1CB41962}"/>
+    <hyperlink ref="A10" r:id="rId24" xr:uid="{F14E50B0-D9C0-48DB-931C-366DA60D26A5}"/>
+    <hyperlink ref="A19" r:id="rId25" xr:uid="{B46CDD11-F539-4CD8-8F01-99911F246E5E}"/>
+    <hyperlink ref="A7" r:id="rId26" xr:uid="{358517C9-F96D-4001-A6D2-2579CAC07395}"/>
+    <hyperlink ref="A22" r:id="rId27" xr:uid="{A1B2AAD9-A8FD-4DBD-8E21-BF758D91F420}"/>
+    <hyperlink ref="A13" r:id="rId28" display="https://upload.wikimedia.org/wikipedia/commons/thumb/4/42/Madonna_and_Child_with_two_Angels_%28by_Filippo_Lippi%29_%E2%80%93_Galleria_degli_Uffizi%2C_Florence.jpg/960px-Madonna_and_Child_with_two_Angels_%28by_Filippo_Lippi%29_%E2%80%93_Galleria_degli_Uffizi%2C_Florence.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A9E81F97-D9BA-4EA8-8D6C-9CA4C0B8E7A9}"/>
+    <hyperlink ref="A26" r:id="rId29" display="https://upload.wikimedia.org/wikipedia/commons/thumb/1/1d/Piero_di_Cosimo_-_Portrait_de_femme_dit_de_Simonetta_Vespucci_-_Google_Art_Project.jpg/960px-Piero_di_Cosimo_-_Portrait_de_femme_dit_de_Simonetta_Vespucci_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{345345A4-5E6D-4024-8651-B74F4AB819D3}"/>
+    <hyperlink ref="A30" r:id="rId30" xr:uid="{13BDD9C7-6E3D-488B-BB3F-79D161E24358}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quizzes/peinture-15e-niveau1.xlsx
+++ b/quizzes/peinture-15e-niveau1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers excel terminés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{91853F78-C565-4C14-9587-130DB9C052B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{88F30EAF-DA1D-4710-9E19-36CA60B9B4B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="212">
   <si>
     <t>image</t>
   </si>
@@ -46,6 +46,9 @@
     <t>Dimensions</t>
   </si>
   <si>
+    <t>Nationalité</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/8e/The_Baptism_of_Christ_%28Verrocchio_%26_Leonardo%29.jpg/1280px-The_Baptism_of_Christ_%28Verrocchio_%26_Leonardo%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -70,6 +73,9 @@
     <t>177 × 151 cm</t>
   </si>
   <si>
+    <t>italienne</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/aa/Mantegna_-_Ducal_Palace%2C_View_of_the_west_and_north_walls%2C_0sposi2.jpg/1280px-Mantegna_-_Ducal_Palace%2C_View_of_the_west_and_north_walls%2C_0sposi2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
   </si>
   <si>
@@ -190,6 +196,9 @@
     <t>vers 1415-1475</t>
   </si>
   <si>
+    <t>flamande (Belgique)</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/91/Birth_of_St_Mary_in_Santa_Maria_Novella_in_Firenze_by_Domenico_Ghirlandaio.jpg/1280px-Birth_of_St_Mary_in_Santa_Maria_Novella_in_Firenze_by_Domenico_Ghirlandaio.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -367,6 +376,9 @@
     <t>82,2 × 60 cm</t>
   </si>
   <si>
+    <t>hollandaise (Pays-Bas)</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/6d/The_Garden_of_Earthly_Delights_by_Bosch_High_Resolution.jpg/1280px-The_Garden_of_Earthly_Delights_by_Bosch_High_Resolution.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -407,6 +419,9 @@
   </si>
   <si>
     <t>132 × 154 cm</t>
+  </si>
+  <si>
+    <t>suisse</t>
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/35/Signorelli_Resurrection.jpg/1280px-Signorelli_Resurrection.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
@@ -1075,7 +1090,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="111.85546875" customWidth="1"/>
@@ -1088,7 +1103,7 @@
     <col min="8" max="8" width="28.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="4" customFormat="1" ht="30" customHeight="1">
+    <row r="1" spans="1:9" s="4" customFormat="1" ht="30" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1113,785 +1128,878 @@
       <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <v>25</v>
+      </c>
+      <c r="I3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="I4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="H5" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="I5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C6" s="8">
         <v>1486</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+        <v>45</v>
+      </c>
+      <c r="I6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="I10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="I11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="I12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="I13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="I14" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="I15" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="I16" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="I17" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="I18" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="I19" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I20" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="I21" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="I22" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="I23" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="I24" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="G25" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="H18" s="7" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="A21" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="G21" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="G22" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="H22" s="7" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="H23" s="7" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8">
-      <c r="A24" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="G24" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="H24" s="7" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>42</v>
-      </c>
       <c r="H25" s="7" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
+        <v>173</v>
+      </c>
+      <c r="I25" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
       <c r="A26" s="5" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C26" s="8">
         <v>1480</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8">
+        <v>179</v>
+      </c>
+      <c r="I26" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
       <c r="A27" s="6" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8">
+        <v>186</v>
+      </c>
+      <c r="I27" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
       <c r="A28" s="6" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8">
+        <v>192</v>
+      </c>
+      <c r="I28" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
       <c r="A29" s="6" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8">
+        <v>199</v>
+      </c>
+      <c r="I29" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
       <c r="A30" s="5" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C30" s="1">
         <v>1472</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="F30" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="G30" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H30" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="I30" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="G31" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="G30" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H30" s="7" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8">
-      <c r="A31" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="F31" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="G31" s="7" t="s">
-        <v>193</v>
-      </c>
       <c r="H31" s="7" t="s">
-        <v>206</v>
+        <v>211</v>
+      </c>
+      <c r="I31" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
